--- a/product_selector_out/STM32WBx5.xlsx
+++ b/product_selector_out/STM32WBx5.xlsx
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6430,14 +6430,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -6555,9 +6555,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD13" s="6" t="inlineStr">
@@ -6600,9 +6600,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM13" s="6" t="inlineStr">
@@ -6660,14 +6660,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ13" s="6" t="inlineStr">
@@ -6750,9 +6750,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6772,14 +6772,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -6897,9 +6897,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD14" s="6" t="inlineStr">
@@ -6942,9 +6942,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM14" s="6" t="inlineStr">
@@ -7002,14 +7002,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -7092,9 +7092,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7114,14 +7114,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -7239,9 +7239,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD15" s="6" t="inlineStr">
@@ -7284,9 +7284,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM15" s="6" t="inlineStr">
@@ -7344,14 +7344,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ15" s="6" t="inlineStr">
@@ -7434,9 +7434,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7456,14 +7456,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -7581,9 +7581,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD16" s="6" t="inlineStr">
@@ -7626,9 +7626,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM16" s="6" t="inlineStr">
@@ -7686,14 +7686,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ16" s="6" t="inlineStr">
@@ -7776,9 +7776,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8140,14 +8140,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -8265,9 +8265,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD18" s="6" t="inlineStr">
@@ -8310,9 +8310,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM18" s="6" t="inlineStr">
@@ -8370,14 +8370,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr">
@@ -8460,9 +8460,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8482,14 +8482,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -8607,9 +8607,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD19" s="6" t="inlineStr">
@@ -8652,9 +8652,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM19" s="6" t="inlineStr">
@@ -8712,14 +8712,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ19" s="6" t="inlineStr">
@@ -8802,9 +8802,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8824,14 +8824,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -8949,9 +8949,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD20" s="6" t="inlineStr">
@@ -8994,9 +8994,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM20" s="6" t="inlineStr">
@@ -9054,14 +9054,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr">
@@ -9144,9 +9144,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9166,14 +9166,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -9291,9 +9291,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD21" s="6" t="inlineStr">
@@ -9336,9 +9336,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM21" s="6" t="inlineStr">
@@ -9396,14 +9396,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ21" s="6" t="inlineStr">
@@ -9486,9 +9486,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9508,14 +9508,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -9633,9 +9633,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD22" s="8" t="inlineStr">
@@ -9678,9 +9678,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM22" s="6" t="inlineStr">
@@ -9738,14 +9738,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ22" s="6" t="inlineStr">
@@ -9828,9 +9828,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9850,14 +9850,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -9975,9 +9975,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD23" s="8" t="inlineStr">
@@ -10020,9 +10020,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM23" s="6" t="inlineStr">
@@ -10080,14 +10080,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ23" s="6" t="inlineStr">
@@ -10170,9 +10170,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10192,14 +10192,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -10317,9 +10317,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD24" s="6" t="inlineStr">
@@ -10362,9 +10362,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM24" s="6" t="inlineStr">
@@ -10422,14 +10422,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ24" s="6" t="inlineStr">
@@ -10512,9 +10512,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10582,14 +10582,14 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Table 21. General operating conditions: V_DD min reads '1.71(1) (2)' — the footnote qualifies the figure</t>
+          <t>Table 21. General operating conditions: V_DD min reads '1.71(1) (2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WB55RC</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10604,14 +10604,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32WB55RC</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -10626,491 +10626,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STM32WB55VG</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32WB55VG</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32WB55VY</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32WB55VY</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32WB55VE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32WB55VE</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32WB55CC</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32WB55CC</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32WB55RE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32WB55RE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32WB55VC</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32WB55VC</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32WB55CG</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32WB55CG</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32WB55RG</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32WB55RG</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the footnote qualifies the figure</t>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32WBx5.xlsx
+++ b/product_selector_out/STM32WBx5.xlsx
@@ -1692,7 +1692,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2376,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -2718,7 +2718,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -4086,7 +4086,7 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -4428,7 +4428,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -5112,7 +5112,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
     </row>
@@ -6430,14 +6430,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -6555,9 +6555,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD13" s="6" t="inlineStr">
@@ -6600,9 +6600,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM13" s="6" t="inlineStr">
@@ -6660,14 +6660,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX13" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY13" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ13" s="6" t="inlineStr">
@@ -6750,9 +6750,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -6772,14 +6772,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -6897,9 +6897,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD14" s="6" t="inlineStr">
@@ -6942,9 +6942,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM14" s="6" t="inlineStr">
@@ -7002,14 +7002,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX14" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY14" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -7092,9 +7092,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7114,14 +7114,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -7239,9 +7239,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD15" s="6" t="inlineStr">
@@ -7284,9 +7284,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM15" s="6" t="inlineStr">
@@ -7344,14 +7344,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX15" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY15" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ15" s="6" t="inlineStr">
@@ -7434,9 +7434,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -7456,14 +7456,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -7581,9 +7581,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD16" s="6" t="inlineStr">
@@ -7626,9 +7626,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM16" s="6" t="inlineStr">
@@ -7686,14 +7686,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX16" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY16" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ16" s="6" t="inlineStr">
@@ -7776,9 +7776,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8140,14 +8140,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -8265,9 +8265,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD18" s="6" t="inlineStr">
@@ -8310,9 +8310,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM18" s="6" t="inlineStr">
@@ -8370,14 +8370,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX18" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY18" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr">
@@ -8460,9 +8460,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8482,14 +8482,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -8607,9 +8607,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD19" s="6" t="inlineStr">
@@ -8652,9 +8652,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM19" s="6" t="inlineStr">
@@ -8712,14 +8712,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX19" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY19" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ19" s="6" t="inlineStr">
@@ -8802,9 +8802,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -8824,14 +8824,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -8949,9 +8949,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD20" s="6" t="inlineStr">
@@ -8994,9 +8994,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM20" s="6" t="inlineStr">
@@ -9054,14 +9054,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX20" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY20" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr">
@@ -9144,9 +9144,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9166,14 +9166,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -9291,9 +9291,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD21" s="6" t="inlineStr">
@@ -9336,9 +9336,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM21" s="6" t="inlineStr">
@@ -9396,14 +9396,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX21" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY21" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ21" s="6" t="inlineStr">
@@ -9486,9 +9486,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9508,14 +9508,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -9633,9 +9633,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD22" s="8" t="inlineStr">
@@ -9678,9 +9678,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM22" s="6" t="inlineStr">
@@ -9738,14 +9738,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX22" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY22" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ22" s="6" t="inlineStr">
@@ -9828,9 +9828,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -9850,14 +9850,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -9975,9 +9975,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD23" s="8" t="inlineStr">
@@ -10020,9 +10020,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM23" s="6" t="inlineStr">
@@ -10080,14 +10080,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX23" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY23" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ23" s="6" t="inlineStr">
@@ -10170,9 +10170,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10192,14 +10192,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="E24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="E24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -10317,9 +10317,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AC24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AD24" s="6" t="inlineStr">
@@ -10362,9 +10362,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AL24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AM24" s="6" t="inlineStr">
@@ -10422,14 +10422,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AY24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="AX24" s="9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="AY24" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
         </is>
       </c>
       <c r="AZ24" s="6" t="inlineStr">
@@ -10512,9 +10512,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="8" t="inlineStr">
-        <is>
-          <t>UNAVAILABLE</t>
+      <c r="BP24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
     </row>
@@ -10533,7 +10533,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10589,7 +10589,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WB55CC</t>
+          <t>STM32WB55RC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10604,27 +10604,511 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>STM32WB55RC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>STM32WB55VG</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>STM32WB55VG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>STM32WB55VY</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>STM32WB55VY</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>STM32WB55VE</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>STM32WB55VE</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>STM32WB55CC</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>STM32WB55CC</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Supply Voltage (V) min</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>AMBIGUOUS</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>STM32WB55RE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>STM32WB55RE</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>STM32WB55VC</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>STM32WB55VC</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>STM32WB55CG</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>STM32WB55CG</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>STM32WB55RG</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>STM32WB55RG</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>STM32WB35CE</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>STM32WB35CE</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>STM32WB35CC</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>STM32WB35CC</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>STM32WB55CE</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Package</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>STM32WB55CE</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Supply Voltage (V) min</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AMBIGUOUS</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
         <is>
           <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32WBx5.xlsx
+++ b/product_selector_out/STM32WBx5.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,11 @@
         <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -105,6 +110,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -2468,7 +2474,7 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>3, 5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
@@ -3494,7 +3500,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>3, 5</t>
+          <t>5</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
@@ -6500,14 +6506,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R13" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S13" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -6842,14 +6848,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R14" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S14" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -7184,14 +7190,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -7526,14 +7532,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R16" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -7868,14 +7874,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -8210,14 +8216,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R18" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S18" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -8552,14 +8558,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R19" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S19" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -8894,14 +8900,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R20" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -9236,14 +9242,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R21" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S21" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -9578,14 +9584,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R22" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -9920,14 +9926,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R23" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S23" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -10262,14 +10268,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="S24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="R24" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">

--- a/product_selector_out/STM32WBx5.xlsx
+++ b/product_selector_out/STM32WBx5.xlsx
@@ -1698,7 +1698,7 @@
       </c>
       <c r="BP13" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2040,7 @@
       </c>
       <c r="BP14" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="BP15" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2474,7 +2474,7 @@
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3, 5</t>
         </is>
       </c>
       <c r="S16" s="4" t="inlineStr">
@@ -2724,7 +2724,7 @@
       </c>
       <c r="BP16" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3408,7 @@
       </c>
       <c r="BP18" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>3, 5</t>
         </is>
       </c>
       <c r="S19" s="4" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BP19" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
       </c>
       <c r="BP20" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4434,7 @@
       </c>
       <c r="BP21" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="BP22" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5118,7 +5118,7 @@
       </c>
       <c r="BP23" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -5460,7 +5460,7 @@
       </c>
       <c r="BP24" s="4" t="inlineStr">
         <is>
-          <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -6436,14 +6436,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F13" s="6" t="inlineStr">
@@ -6506,14 +6506,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R13" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S13" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T13" s="6" t="inlineStr">
@@ -6561,9 +6561,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD13" s="6" t="inlineStr">
@@ -6606,9 +6606,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM13" s="6" t="inlineStr">
@@ -6666,14 +6666,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX13" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY13" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY13" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ13" s="6" t="inlineStr">
@@ -6756,9 +6756,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP13" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -6778,14 +6778,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F14" s="6" t="inlineStr">
@@ -6848,14 +6848,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R14" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S14" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T14" s="6" t="inlineStr">
@@ -6903,9 +6903,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD14" s="6" t="inlineStr">
@@ -6948,9 +6948,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM14" s="6" t="inlineStr">
@@ -7008,14 +7008,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX14" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY14" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY14" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ14" s="6" t="inlineStr">
@@ -7098,9 +7098,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP14" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7120,14 +7120,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F15" s="6" t="inlineStr">
@@ -7190,14 +7190,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R15" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S15" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -7245,9 +7245,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD15" s="6" t="inlineStr">
@@ -7290,9 +7290,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM15" s="6" t="inlineStr">
@@ -7350,14 +7350,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX15" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY15" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ15" s="6" t="inlineStr">
@@ -7440,9 +7440,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -7462,14 +7462,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F16" s="6" t="inlineStr">
@@ -7532,14 +7532,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R16" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S16" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -7587,9 +7587,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD16" s="6" t="inlineStr">
@@ -7632,9 +7632,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM16" s="6" t="inlineStr">
@@ -7692,14 +7692,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX16" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY16" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ16" s="6" t="inlineStr">
@@ -7782,9 +7782,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8146,14 +8146,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F18" s="6" t="inlineStr">
@@ -8216,14 +8216,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R18" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S18" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T18" s="6" t="inlineStr">
@@ -8271,9 +8271,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD18" s="6" t="inlineStr">
@@ -8316,9 +8316,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM18" s="6" t="inlineStr">
@@ -8376,14 +8376,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX18" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY18" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY18" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ18" s="6" t="inlineStr">
@@ -8466,9 +8466,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP18" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8488,14 +8488,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F19" s="6" t="inlineStr">
@@ -8558,14 +8558,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R19" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S19" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T19" s="6" t="inlineStr">
@@ -8613,9 +8613,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD19" s="6" t="inlineStr">
@@ -8658,9 +8658,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM19" s="6" t="inlineStr">
@@ -8718,14 +8718,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX19" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY19" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY19" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ19" s="6" t="inlineStr">
@@ -8808,9 +8808,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP19" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -8830,14 +8830,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F20" s="6" t="inlineStr">
@@ -8900,14 +8900,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R20" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S20" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -8955,9 +8955,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD20" s="6" t="inlineStr">
@@ -9000,9 +9000,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM20" s="6" t="inlineStr">
@@ -9060,14 +9060,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX20" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY20" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ20" s="6" t="inlineStr">
@@ -9150,9 +9150,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9172,14 +9172,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F21" s="6" t="inlineStr">
@@ -9242,14 +9242,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R21" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S21" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T21" s="6" t="inlineStr">
@@ -9297,9 +9297,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD21" s="6" t="inlineStr">
@@ -9342,9 +9342,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM21" s="6" t="inlineStr">
@@ -9402,14 +9402,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX21" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY21" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY21" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ21" s="6" t="inlineStr">
@@ -9492,9 +9492,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP21" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9514,14 +9514,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -9584,14 +9584,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R22" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S22" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -9639,9 +9639,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD22" s="8" t="inlineStr">
@@ -9684,9 +9684,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM22" s="6" t="inlineStr">
@@ -9744,14 +9744,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX22" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY22" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ22" s="6" t="inlineStr">
@@ -9834,9 +9834,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -9856,14 +9856,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F23" s="6" t="inlineStr">
@@ -9926,14 +9926,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R23" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S23" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T23" s="6" t="inlineStr">
@@ -9981,9 +9981,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD23" s="8" t="inlineStr">
@@ -10026,9 +10026,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM23" s="6" t="inlineStr">
@@ -10086,14 +10086,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX23" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY23" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY23" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ23" s="6" t="inlineStr">
@@ -10176,9 +10176,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP23" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10198,14 +10198,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="F24" s="6" t="inlineStr">
@@ -10268,14 +10268,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R24" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
-        </is>
-      </c>
-      <c r="S24" s="10" t="inlineStr">
-        <is>
-          <t>DERIVED</t>
+      <c r="R24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="S24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -10323,9 +10323,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AC24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AC24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AD24" s="6" t="inlineStr">
@@ -10368,9 +10368,9 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AL24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AL24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM24" s="6" t="inlineStr">
@@ -10428,14 +10428,14 @@
           <t>API</t>
         </is>
       </c>
-      <c r="AX24" s="9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="AY24" s="7" t="inlineStr">
-        <is>
-          <t>DATASHEET</t>
+      <c r="AX24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
+        </is>
+      </c>
+      <c r="AY24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AZ24" s="6" t="inlineStr">
@@ -10518,9 +10518,9 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
+      <c r="BP24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
         </is>
       </c>
     </row>
@@ -10539,7 +10539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -10595,7 +10595,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32WB55RC</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -10610,14 +10610,14 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32WB55RC</t>
+          <t>STM32WB55CC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -10631,490 +10631,6 @@
         </is>
       </c>
       <c r="D4" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>STM32WB55VG</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>STM32WB55VG</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>STM32WB55VY</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>STM32WB55VY</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>STM32WB55VE</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STM32WB55VE</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>STM32WB55CC</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>STM32WB55CC</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>STM32WB55RE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>STM32WB55RE</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>STM32WB55VC</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, WLCSP100 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>STM32WB55VC</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>STM32WB55CG</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>STM32WB55CG</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>STM32WB55RG</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.4 mm pitch, 8 mm x 8 mm, VFQFPN68, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>STM32WB55RG</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>STM32WB35CE</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32WB35CC</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 2 . STM32WB55xx and STM32WB35xx devices features and peripheral counts lists 0.5 mm pitch, 7 mm x 7 mm, UFQFPN48, solder pad for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32WB55CE</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Supply Voltage (V) min</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
         <is>
           <t>Table 24. General operating conditions: V_DD min reads '1.71(1)(2)' — the figure is qualified or corrupted by a footnote</t>
         </is>

--- a/product_selector_out/STM32WBx5.xlsx
+++ b/product_selector_out/STM32WBx5.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP24"/>
+  <dimension ref="A1:BQ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13.26171875" customWidth="1" min="1" max="1"/>
@@ -576,7 +576,8 @@
     <col width="21.984375" customWidth="1" min="65" max="65"/>
     <col width="18" customWidth="1" min="66" max="66"/>
     <col width="18" customWidth="1" min="67" max="67"/>
-    <col width="52" customWidth="1" min="68" max="68"/>
+    <col width="18" customWidth="1" min="68" max="68"/>
+    <col width="52" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -919,6 +920,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -1017,6 +1023,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1356,6 +1363,11 @@
       </c>
       <c r="BP12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BQ12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb15cc.pdf</t>
         </is>
       </c>
@@ -1701,6 +1713,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ13" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="inlineStr">
@@ -2043,6 +2060,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ14" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="inlineStr">
@@ -2385,6 +2407,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ15" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="inlineStr">
@@ -2727,6 +2754,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ16" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="inlineStr">
@@ -3066,6 +3098,11 @@
       </c>
       <c r="BP17" s="4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="BQ17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32wb55cc.pdf</t>
         </is>
       </c>
@@ -3411,6 +3448,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ18" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="inlineStr">
@@ -3753,6 +3795,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ19" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="inlineStr">
@@ -4095,6 +4142,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ20" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="inlineStr">
@@ -4437,6 +4489,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ21" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
@@ -4779,6 +4836,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ22" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="inlineStr">
@@ -5121,6 +5183,11 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ23" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="inlineStr">
@@ -5463,9 +5530,14 @@
           <t>-</t>
         </is>
       </c>
+      <c r="BQ24" s="4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="67">
+  <mergeCells count="68">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -5488,14 +5560,13 @@
     <mergeCell ref="Q10:Q11"/>
     <mergeCell ref="AR10:AR11"/>
     <mergeCell ref="AT10:AT11"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="A1:BP8"/>
     <mergeCell ref="AV10:AV11"/>
     <mergeCell ref="BB10:BB11"/>
     <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -5513,6 +5584,7 @@
     <mergeCell ref="BP10:BP11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A9:BQ9"/>
     <mergeCell ref="I10:I11"/>
     <mergeCell ref="AL10:AL11"/>
     <mergeCell ref="K10:K11"/>
@@ -5525,6 +5597,7 @@
     <mergeCell ref="AX10:AX11"/>
     <mergeCell ref="AZ10:AZ11"/>
     <mergeCell ref="BF10:BF11"/>
+    <mergeCell ref="BQ10:BQ11"/>
     <mergeCell ref="R10:R11"/>
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="BO10:BO11"/>
@@ -5560,7 +5633,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BP24"/>
+  <dimension ref="A1:BQ24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -5631,6 +5704,7 @@
     <col width="16" customWidth="1" min="66" max="66"/>
     <col width="16" customWidth="1" min="67" max="67"/>
     <col width="16" customWidth="1" min="68" max="68"/>
+    <col width="16" customWidth="1" min="69" max="69"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5979,6 +6053,11 @@
         </is>
       </c>
       <c r="BP10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BQ10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -6077,6 +6156,7 @@
       <c r="BN11" s="2" t="n"/>
       <c r="BO11" s="2" t="n"/>
       <c r="BP11" s="2" t="n"/>
+      <c r="BQ11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -6414,7 +6494,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP12" s="6" t="inlineStr">
+      <c r="BP12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BQ12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -6761,6 +6846,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
@@ -7103,6 +7193,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -7445,6 +7540,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -7787,6 +7887,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -8124,7 +8229,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BP17" s="6" t="inlineStr">
+      <c r="BP17" s="7" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="BQ17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8471,6 +8581,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -8813,6 +8928,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -9155,6 +9275,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="6" t="inlineStr">
@@ -9497,6 +9622,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -9839,6 +9969,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -10181,6 +10316,11 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -10523,11 +10663,16 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
+      <c r="BQ24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A1:BP8"/>
-    <mergeCell ref="A9:BP9"/>
+    <mergeCell ref="A1:BQ8"/>
+    <mergeCell ref="A9:BQ9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
